--- a/Network/2.xlsx
+++ b/Network/2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\final-project-2025-26\Network\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github Repo\final-project-2025-26\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFEF508-C361-4DF5-B085-EC5992F80579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F4E0BB-E61E-4E47-A851-DEB940802D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="27540" windowHeight="10080" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{6F35F872-ABCC-42C2-B031-C1DE53122CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
   <si>
     <t>Név</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>MSSQL Cluster IP</t>
+  </si>
+  <si>
+    <t>yeah</t>
   </si>
 </sst>
 </file>
@@ -460,9 +463,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +503,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -606,7 +609,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -748,7 +751,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1036,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D6D1D5-74AF-4AB6-A0A1-6D17E92BA017}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1235,6 +1238,11 @@
         <v>70</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
